--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.84686831333017</v>
+        <v>4.525116100916152</v>
       </c>
       <c r="D2" t="n">
-        <v>24.53033514223756</v>
+        <v>3.986179460613603</v>
       </c>
       <c r="E2" t="n">
-        <v>9.425101503197711</v>
+        <v>1.531578994269628</v>
       </c>
       <c r="F2" t="n">
-        <v>4.561289950107655</v>
+        <v>0.7412096168924941</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.261607127464751</v>
+        <v>1.017511158213022</v>
       </c>
       <c r="D3" t="n">
-        <v>13.5041145993031</v>
+        <v>2.194418622386754</v>
       </c>
       <c r="E3" t="n">
-        <v>9.425101503197711</v>
+        <v>1.531578994269628</v>
       </c>
       <c r="F3" t="n">
-        <v>4.561289950107655</v>
+        <v>0.7412096168924941</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.50552199553979</v>
+        <v>4.957147324275216</v>
       </c>
       <c r="D4" t="n">
-        <v>24.81231548275036</v>
+        <v>4.032001265946934</v>
       </c>
       <c r="E4" t="n">
-        <v>9.425101503197711</v>
+        <v>1.531578994269628</v>
       </c>
       <c r="F4" t="n">
-        <v>4.561289950107655</v>
+        <v>0.7412096168924941</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.01322416714197</v>
+        <v>3.25214892716057</v>
       </c>
       <c r="D5" t="n">
-        <v>20.70677163814345</v>
+        <v>3.36485039119831</v>
       </c>
       <c r="E5" t="n">
-        <v>9.425101503197711</v>
+        <v>1.531578994269628</v>
       </c>
       <c r="F5" t="n">
-        <v>4.561289950107655</v>
+        <v>0.7412096168924941</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
